--- a/Pivot.xlsx
+++ b/Pivot.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{675ADBC9-B0B3-4731-A960-79B0C9708138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A12DAAE-EC04-4C56-BA37-E31317EF9573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E1CB22F-35E4-498A-9D36-5D808F9EB48B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet4" sheetId="1" r:id="rId1"/>
+    <sheet name="Pivot" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Pivot.xlsx
+++ b/Pivot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A12DAAE-EC04-4C56-BA37-E31317EF9573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A64F895-FB85-457B-AFFF-06ED49ECFD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E1CB22F-35E4-498A-9D36-5D808F9EB48B}"/>
   </bookViews>
@@ -481,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4BE1A5-87CB-49F0-A315-8CAB5D69E353}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -489,7 +489,7 @@
     <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -672,6 +672,12 @@
         <v>3500</v>
       </c>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <f>SUM(F2:F9)</f>
+        <v>191000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Pivot.xlsx
+++ b/Pivot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A64F895-FB85-457B-AFFF-06ED49ECFD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE7A9BF-8A3C-4E3E-B801-40E650A00BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E1CB22F-35E4-498A-9D36-5D808F9EB48B}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Pivot" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="14" r:id="rId2"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
   <si>
     <t>East</t>
   </si>
@@ -96,6 +99,15 @@
   </si>
   <si>
     <t>Order ID</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Sales</t>
   </si>
 </sst>
 </file>
@@ -139,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -147,6 +159,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -162,6 +179,160 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Suraj S P" refreshedDate="46126.489681481478" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{93CC7255-8C7A-4EA9-978B-9BABF024CCD3}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:F9" sheet="Pivot"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="Order ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="8"/>
+    </cacheField>
+    <cacheField name="Date" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Electronics"/>
+        <s v="Accessories"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Sales" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2000" maxValue="60000"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="8">
+  <r>
+    <n v="1"/>
+    <s v="Jan"/>
+    <s v="Laptop"/>
+    <x v="0"/>
+    <s v="South"/>
+    <n v="50000"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <s v="Jan"/>
+    <s v="Mouse"/>
+    <x v="1"/>
+    <s v="North"/>
+    <n v="2000"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <s v="Feb"/>
+    <s v="Laptop"/>
+    <x v="0"/>
+    <s v="South"/>
+    <n v="60000"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <s v="Feb"/>
+    <s v="Keyboard"/>
+    <x v="1"/>
+    <s v="East"/>
+    <n v="3000"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <s v="Mar"/>
+    <s v="Monitor"/>
+    <x v="0"/>
+    <s v="West"/>
+    <n v="15000"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <s v="Mar"/>
+    <s v="Mouse"/>
+    <x v="1"/>
+    <s v="South"/>
+    <n v="2500"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <s v="Apr"/>
+    <s v="Laptop"/>
+    <x v="0"/>
+    <s v="North"/>
+    <n v="55000"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <s v="Apr"/>
+    <s v="Keyboard"/>
+    <x v="1"/>
+    <s v="East"/>
+    <n v="3500"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E30948A-A8B4-4BC3-8028-6B586A5D90AB}" name="PivotTable4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H1:I4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -481,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4BE1A5-87CB-49F0-A315-8CAB5D69E353}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -490,9 +661,11 @@
     <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -511,8 +684,14 @@
       <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -531,8 +710,14 @@
       <c r="F2" s="1">
         <v>50000</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -551,8 +736,14 @@
       <c r="F3" s="1">
         <v>2000</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -571,8 +762,14 @@
       <c r="F4" s="1">
         <v>60000</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="5">
+        <v>191000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -592,7 +789,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -612,7 +809,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -632,7 +829,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -652,7 +849,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -672,7 +869,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F10">
         <f>SUM(F2:F9)</f>
         <v>191000</v>

--- a/Pivot.xlsx
+++ b/Pivot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE7A9BF-8A3C-4E3E-B801-40E650A00BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B98284C-2E11-4B3E-8643-D6BD6E135BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E1CB22F-35E4-498A-9D36-5D808F9EB48B}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="14" r:id="rId2"/>
+    <pivotCache cacheId="15" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="23">
   <si>
     <t>East</t>
   </si>
@@ -203,7 +203,12 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Region" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="4">
+        <s v="South"/>
+        <s v="North"/>
+        <s v="East"/>
+        <s v="West"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Sales" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2000" maxValue="60000"/>
@@ -224,7 +229,7 @@
     <s v="Jan"/>
     <s v="Laptop"/>
     <x v="0"/>
-    <s v="South"/>
+    <x v="0"/>
     <n v="50000"/>
   </r>
   <r>
@@ -232,7 +237,7 @@
     <s v="Jan"/>
     <s v="Mouse"/>
     <x v="1"/>
-    <s v="North"/>
+    <x v="1"/>
     <n v="2000"/>
   </r>
   <r>
@@ -240,7 +245,7 @@
     <s v="Feb"/>
     <s v="Laptop"/>
     <x v="0"/>
-    <s v="South"/>
+    <x v="0"/>
     <n v="60000"/>
   </r>
   <r>
@@ -248,7 +253,7 @@
     <s v="Feb"/>
     <s v="Keyboard"/>
     <x v="1"/>
-    <s v="East"/>
+    <x v="2"/>
     <n v="3000"/>
   </r>
   <r>
@@ -256,7 +261,7 @@
     <s v="Mar"/>
     <s v="Monitor"/>
     <x v="0"/>
-    <s v="West"/>
+    <x v="3"/>
     <n v="15000"/>
   </r>
   <r>
@@ -264,7 +269,7 @@
     <s v="Mar"/>
     <s v="Mouse"/>
     <x v="1"/>
-    <s v="South"/>
+    <x v="0"/>
     <n v="2500"/>
   </r>
   <r>
@@ -272,7 +277,7 @@
     <s v="Apr"/>
     <s v="Laptop"/>
     <x v="0"/>
-    <s v="North"/>
+    <x v="1"/>
     <n v="55000"/>
   </r>
   <r>
@@ -280,20 +285,83 @@
     <s v="Apr"/>
     <s v="Keyboard"/>
     <x v="1"/>
-    <s v="East"/>
+    <x v="2"/>
     <n v="3500"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E30948A-A8B4-4BC3-8028-6B586A5D90AB}" name="PivotTable4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42BA5457-B420-4D10-AC97-D174FF55EE6B}" name="PivotTable6" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H6:I11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E30948A-A8B4-4BC3-8028-6B586A5D90AB}" name="PivotTable4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H1:I4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="3">
         <item x="1"/>
         <item x="0"/>
@@ -652,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4BE1A5-87CB-49F0-A315-8CAB5D69E353}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -808,6 +876,12 @@
       <c r="F6" s="1">
         <v>15000</v>
       </c>
+      <c r="H6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
@@ -828,6 +902,12 @@
       <c r="F7" s="1">
         <v>2500</v>
       </c>
+      <c r="H7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>6500</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
@@ -848,6 +928,12 @@
       <c r="F8" s="1">
         <v>55000</v>
       </c>
+      <c r="H8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="5">
+        <v>57000</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
@@ -867,6 +953,12 @@
       </c>
       <c r="F9" s="1">
         <v>3500</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="5">
+        <v>112500</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -874,6 +966,20 @@
         <f>SUM(F2:F9)</f>
         <v>191000</v>
       </c>
+      <c r="H10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="5">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="5">
+        <v>191000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Pivot.xlsx
+++ b/Pivot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B98284C-2E11-4B3E-8643-D6BD6E135BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97859767-1331-4B93-91B7-D5C2D785E22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E1CB22F-35E4-498A-9D36-5D808F9EB48B}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId2"/>
+    <pivotCache cacheId="16" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="23">
   <si>
     <t>East</t>
   </si>
@@ -181,6 +181,1139 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Pivot.xlsx]Pivot!PivotTable7</c:name>
+    <c:fmtId val="12"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="31750" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="17"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Pivot!$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="31750" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="17"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Pivot!$A$13:$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Pivot!$B$13:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>52000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>63000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>58500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EFD6-4CA3-9CEC-2191B0A65404}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="779382895"/>
+        <c:axId val="1112207167"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="779382895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1112207167"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1112207167"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="95000"/>
+                      <a:lumOff val="5000"/>
+                      <a:alpha val="42000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                      <a:alpha val="36000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="779382895"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="228">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="17"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1688F9FF-D20F-9996-95FB-16FB3BB1FDDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Suraj S P" refreshedDate="46126.489681481478" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="8" xr:uid="{93CC7255-8C7A-4EA9-978B-9BABF024CCD3}">
   <cacheSource type="worksheet">
@@ -191,7 +1324,12 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="8"/>
     </cacheField>
     <cacheField name="Date" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="4">
+        <s v="Jan"/>
+        <s v="Feb"/>
+        <s v="Mar"/>
+        <s v="Apr"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Product" numFmtId="0">
       <sharedItems/>
@@ -226,7 +1364,7 @@
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="8">
   <r>
     <n v="1"/>
-    <s v="Jan"/>
+    <x v="0"/>
     <s v="Laptop"/>
     <x v="0"/>
     <x v="0"/>
@@ -234,7 +1372,7 @@
   </r>
   <r>
     <n v="2"/>
-    <s v="Jan"/>
+    <x v="0"/>
     <s v="Mouse"/>
     <x v="1"/>
     <x v="1"/>
@@ -242,7 +1380,7 @@
   </r>
   <r>
     <n v="3"/>
-    <s v="Feb"/>
+    <x v="1"/>
     <s v="Laptop"/>
     <x v="0"/>
     <x v="0"/>
@@ -250,7 +1388,7 @@
   </r>
   <r>
     <n v="4"/>
-    <s v="Feb"/>
+    <x v="1"/>
     <s v="Keyboard"/>
     <x v="1"/>
     <x v="2"/>
@@ -258,7 +1396,7 @@
   </r>
   <r>
     <n v="5"/>
-    <s v="Mar"/>
+    <x v="2"/>
     <s v="Monitor"/>
     <x v="0"/>
     <x v="3"/>
@@ -266,7 +1404,7 @@
   </r>
   <r>
     <n v="6"/>
-    <s v="Mar"/>
+    <x v="2"/>
     <s v="Mouse"/>
     <x v="1"/>
     <x v="0"/>
@@ -274,7 +1412,7 @@
   </r>
   <r>
     <n v="7"/>
-    <s v="Apr"/>
+    <x v="3"/>
     <s v="Laptop"/>
     <x v="0"/>
     <x v="1"/>
@@ -282,7 +1420,7 @@
   </r>
   <r>
     <n v="8"/>
-    <s v="Apr"/>
+    <x v="3"/>
     <s v="Keyboard"/>
     <x v="1"/>
     <x v="2"/>
@@ -292,7 +1430,89 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42BA5457-B420-4D10-AC97-D174FF55EE6B}" name="PivotTable6" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEBE67DB-AA22-4FAC-9137-332A7AE69271}" name="PivotTable7" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+  <location ref="A12:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" sortType="ascending">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="12" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42BA5457-B420-4D10-AC97-D174FF55EE6B}" name="PivotTable6" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H6:I11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -354,8 +1574,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E30948A-A8B4-4BC3-8028-6B586A5D90AB}" name="PivotTable4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E30948A-A8B4-4BC3-8028-6B586A5D90AB}" name="PivotTable4" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H1:I4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -720,11 +1940,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4BE1A5-87CB-49F0-A315-8CAB5D69E353}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
@@ -981,7 +2201,56 @@
         <v>191000</v>
       </c>
     </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="5">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5">
+        <v>63000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="5">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="5">
+        <v>58500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="5">
+        <v>191000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
--- a/Pivot.xlsx
+++ b/Pivot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97859767-1331-4B93-91B7-D5C2D785E22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8D4BA7-67C5-4C9D-ADEE-D6BA25B20104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E1CB22F-35E4-498A-9D36-5D808F9EB48B}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="16" r:id="rId2"/>
+    <pivotCache cacheId="17" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="23">
   <si>
     <t>East</t>
   </si>
@@ -1332,7 +1332,12 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Product" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="4">
+        <s v="Laptop"/>
+        <s v="Mouse"/>
+        <s v="Keyboard"/>
+        <s v="Monitor"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Category" numFmtId="0">
       <sharedItems count="2">
@@ -1365,7 +1370,7 @@
   <r>
     <n v="1"/>
     <x v="0"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <n v="50000"/>
@@ -1373,7 +1378,7 @@
   <r>
     <n v="2"/>
     <x v="0"/>
-    <s v="Mouse"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="1"/>
     <n v="2000"/>
@@ -1381,7 +1386,7 @@
   <r>
     <n v="3"/>
     <x v="1"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <n v="60000"/>
@@ -1389,7 +1394,7 @@
   <r>
     <n v="4"/>
     <x v="1"/>
-    <s v="Keyboard"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="2"/>
     <n v="3000"/>
@@ -1397,7 +1402,7 @@
   <r>
     <n v="5"/>
     <x v="2"/>
-    <s v="Monitor"/>
+    <x v="3"/>
     <x v="0"/>
     <x v="3"/>
     <n v="15000"/>
@@ -1405,7 +1410,7 @@
   <r>
     <n v="6"/>
     <x v="2"/>
-    <s v="Mouse"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <n v="2500"/>
@@ -1413,7 +1418,7 @@
   <r>
     <n v="7"/>
     <x v="3"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <n v="55000"/>
@@ -1421,7 +1426,7 @@
   <r>
     <n v="8"/>
     <x v="3"/>
-    <s v="Keyboard"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="2"/>
     <n v="3500"/>
@@ -1430,7 +1435,87 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEBE67DB-AA22-4FAC-9137-332A7AE69271}" name="PivotTable7" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39F45A9D-CACE-471F-9786-14FFBA791AF1}" name="PivotTable8" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="K1:L6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" sortType="ascending">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="2" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="14" filterVal="14"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEBE67DB-AA22-4FAC-9137-332A7AE69271}" name="PivotTable7" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
   <location ref="A12:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -1511,8 +1596,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42BA5457-B420-4D10-AC97-D174FF55EE6B}" name="PivotTable6" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42BA5457-B420-4D10-AC97-D174FF55EE6B}" name="PivotTable6" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H6:I11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -1574,8 +1659,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E30948A-A8B4-4BC3-8028-6B586A5D90AB}" name="PivotTable4" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E30948A-A8B4-4BC3-8028-6B586A5D90AB}" name="PivotTable4" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H1:I4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -1940,7 +2025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4BE1A5-87CB-49F0-A315-8CAB5D69E353}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1951,9 +2036,11 @@
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -1978,8 +2065,14 @@
       <c r="I1" t="s">
         <v>22</v>
       </c>
+      <c r="K1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2004,8 +2097,14 @@
       <c r="I2" s="5">
         <v>11000</v>
       </c>
+      <c r="K2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="5">
+        <v>6500</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2030,8 +2129,14 @@
       <c r="I3" s="5">
         <v>180000</v>
       </c>
+      <c r="K3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5">
+        <v>165000</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2056,8 +2161,14 @@
       <c r="I4" s="5">
         <v>191000</v>
       </c>
+      <c r="K4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="5">
+        <v>15000</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2076,8 +2187,14 @@
       <c r="F5" s="1">
         <v>3000</v>
       </c>
+      <c r="K5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L5" s="5">
+        <v>4500</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2102,8 +2219,14 @@
       <c r="I6" t="s">
         <v>22</v>
       </c>
+      <c r="K6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="5">
+        <v>191000</v>
+      </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2129,7 +2252,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2155,7 +2278,7 @@
         <v>57000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2181,7 +2304,7 @@
         <v>112500</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F10">
         <f>SUM(F2:F9)</f>
         <v>191000</v>
@@ -2193,7 +2316,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H11" s="4" t="s">
         <v>21</v>
       </c>
@@ -2201,7 +2324,7 @@
         <v>191000</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -2209,7 +2332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -2217,7 +2340,7 @@
         <v>52000</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
@@ -2225,7 +2348,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
@@ -2233,7 +2356,7 @@
         <v>17500</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>3</v>
       </c>
@@ -2251,6 +2374,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
--- a/Pivot.xlsx
+++ b/Pivot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8D4BA7-67C5-4C9D-ADEE-D6BA25B20104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BE50F3-A828-478F-BD3E-C187FE1F1B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E1CB22F-35E4-498A-9D36-5D808F9EB48B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
   <si>
     <t>East</t>
   </si>
@@ -108,6 +108,21 @@
   </si>
   <si>
     <t>Sum of Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business Insights </t>
+  </si>
+  <si>
+    <t>East Region needs more improvements</t>
+  </si>
+  <si>
+    <t>In March there is a Dip in sales</t>
+  </si>
+  <si>
+    <t>Electronics Category has Strong Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">from above insights  the company should take measure in "mouse"  product and have to do more promotion in east region  </t>
   </si>
 </sst>
 </file>
@@ -151,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -164,6 +179,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -213,11 +229,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -234,7 +250,7 @@
       <c:pivotFmt>
         <c:idx val="0"/>
         <c:spPr>
-          <a:ln w="31750" cap="rnd">
+          <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
             </a:solidFill>
@@ -244,13 +260,15 @@
         </c:spPr>
         <c:marker>
           <c:symbol val="circle"/>
-          <c:size val="17"/>
+          <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -271,9 +289,12 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -316,7 +337,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="31750" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -326,13 +347,15 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="17"/>
+            <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -352,9 +375,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="lt1"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -377,13 +403,14 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525">
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
                       <a:solidFill>
-                        <a:schemeClr val="dk1">
-                          <a:lumMod val="50000"/>
-                          <a:lumOff val="50000"/>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
+                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -466,11 +493,11 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="dk1">
-                <a:lumMod val="75000"/>
-                <a:lumOff val="25000"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -482,11 +509,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -509,29 +536,17 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="95000"/>
-                      <a:lumOff val="5000"/>
-                      <a:alpha val="42000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="0">
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="75000"/>
-                      <a:alpha val="36000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -541,6 +556,33 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="779382895"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
@@ -557,12 +599,7 @@
       <c:legendPos val="r"/>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="39000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -575,9 +612,9 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -601,30 +638,14 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="lt1"/>
-        </a:gs>
-        <a:gs pos="39000">
-          <a:schemeClr val="lt1"/>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="lt1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="25000"/>
-          <a:lumOff val="75000"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
@@ -706,174 +727,146 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="228">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="39000">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="lt1">
-              <a:lumMod val="75000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
         <a:solidFill>
           <a:schemeClr val="dk1">
             <a:lumMod val="25000"/>
             <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-          <a:alpha val="75000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="phClr"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
     </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="phClr"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
     </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="31750" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -882,29 +875,36 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="17"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -920,19 +920,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -947,13 +949,13 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
@@ -966,17 +968,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -985,12 +987,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
@@ -1004,36 +1006,30 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
@@ -1043,28 +1039,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -1073,88 +1058,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1">
-          <a:lumMod val="95000"/>
-          <a:alpha val="39000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="75000"/>
             <a:lumOff val="25000"/>
           </a:schemeClr>
@@ -1162,6 +1071,64 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -1169,14 +1136,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1188,12 +1155,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -1202,13 +1169,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -1217,9 +1185,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1237,9 +1205,9 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -1250,25 +1218,26 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
     <cs:spPr>
+      <a:noFill/>
       <a:ln>
         <a:noFill/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -1515,7 +1484,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEBE67DB-AA22-4FAC-9137-332A7AE69271}" name="PivotTable7" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEBE67DB-AA22-4FAC-9137-332A7AE69271}" name="PivotTable7" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
   <location ref="A12:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -2025,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4BE1A5-87CB-49F0-A315-8CAB5D69E353}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2038,9 +2007,10 @@
     <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="98.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -2071,8 +2041,11 @@
       <c r="L1" t="s">
         <v>22</v>
       </c>
+      <c r="N1" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2103,8 +2076,11 @@
       <c r="L2" s="5">
         <v>6500</v>
       </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2135,8 +2111,11 @@
       <c r="L3" s="5">
         <v>165000</v>
       </c>
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2167,8 +2146,11 @@
       <c r="L4" s="5">
         <v>15000</v>
       </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2193,8 +2175,11 @@
       <c r="L5" s="5">
         <v>4500</v>
       </c>
+      <c r="N5" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2226,7 +2211,7 @@
         <v>191000</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2252,7 +2237,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2278,7 +2263,7 @@
         <v>57000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2304,7 +2289,7 @@
         <v>112500</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F10">
         <f>SUM(F2:F9)</f>
         <v>191000</v>
@@ -2316,7 +2301,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="H11" s="4" t="s">
         <v>21</v>
       </c>
@@ -2324,7 +2309,7 @@
         <v>191000</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -2332,7 +2317,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -2340,7 +2325,7 @@
         <v>52000</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
@@ -2348,7 +2333,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
@@ -2356,7 +2341,7 @@
         <v>17500</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>3</v>
       </c>
